--- a/toolkit/programme-charter.xlsx
+++ b/toolkit/programme-charter.xlsx
@@ -552,6 +552,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -564,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -654,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -744,6 +747,7 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -836,6 +840,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
@@ -912,6 +917,7 @@
       </c>
       <c r="C37" s="8" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
@@ -971,6 +977,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -1186,10 +1193,11 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Worked example, year 2 (Module 12): funnel coverage 64%, cost visibility 83%, 41% of approved ideas implemented, £1.9M of checked savings a quarter, average payback 8.2 months.</t>
+          <t>Worked example, year 2 (Module 12): funnel coverage 64%, cost visibility 83%, 68% of approved ideas implemented, £1.9M of checked savings a quarter, average payback 8.2 months.</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1264,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -1552,6 +1561,7 @@
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
